--- a/output/Test_Cases_collection/TC20 - Verify Navigation to All Items from Sideb.xlsx
+++ b/output/Test_Cases_collection/TC20 - Verify Navigation to All Items from Sideb.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
   <si>
     <t>Test Case Name</t>
   </si>
@@ -58,40 +58,46 @@
     <t>5</t>
   </si>
   <si>
-    <t>Launch the application and open [https://www.saucedemo.com/]</t>
-  </si>
-  <si>
-    <t>Enter "standard_user" in the "user-name" field.</t>
-  </si>
-  <si>
-    <t>Enter "secret_sauce" in the "password" field.</t>
-  </si>
-  <si>
-    <t>Click on "login-button".</t>
-  </si>
-  <si>
-    <t>Click on "react-burger-menu-btn".</t>
-  </si>
-  <si>
-    <t>Change the value to "All Items" in "inventory_sidebar_link".</t>
-  </si>
-  <si>
-    <t>The login page is displayed.</t>
-  </si>
-  <si>
-    <t>The username is entered in the field.</t>
-  </si>
-  <si>
-    <t>The password is entered in the field.</t>
-  </si>
-  <si>
-    <t>The inventory page is displayed.</t>
-  </si>
-  <si>
-    <t>The sidebar menu is displayed.</t>
-  </si>
-  <si>
-    <t>The inventory page is displayed with all items listed.</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Launch the application and open `https://www.saucedemo.com/`</t>
+  </si>
+  <si>
+    <t>Enter "standard_user" in the "user-name" field</t>
+  </si>
+  <si>
+    <t>Enter "secret_sauce" in the "password" field</t>
+  </si>
+  <si>
+    <t>Click on "login-button"</t>
+  </si>
+  <si>
+    <t>Click on "react-burger-menu-btn"</t>
+  </si>
+  <si>
+    <t>Select "All Items" from "inventory_sidebar_link"</t>
+  </si>
+  <si>
+    <t>Verify that all products are displayed on the inventory page</t>
+  </si>
+  <si>
+    <t>Login page is displayed</t>
+  </si>
+  <si>
+    <t>Username is entered in the field</t>
+  </si>
+  <si>
+    <t>Password is entered in the field</t>
+  </si>
+  <si>
+    <t>User is redirected to the inventory page</t>
+  </si>
+  <si>
+    <t>Sidebar menu is displayed</t>
+  </si>
+  <si>
+    <t>All products are visible on the inventory page</t>
   </si>
   <si>
     <t>New</t>
@@ -100,7 +106,7 @@
     <t>Manual</t>
   </si>
   <si>
-    <t>Workflow</t>
+    <t>UI</t>
   </si>
 </sst>
 </file>
@@ -458,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -492,19 +498,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -515,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -535,16 +541,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -555,16 +561,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -575,16 +581,16 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -595,16 +601,36 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
         <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
